--- a/Result/profitability/9924.xlsx
+++ b/Result/profitability/9924.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7425</v>
+        <v>0.6712499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>21.5075</v>
+        <v>20.70875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0.59375</v>
+        <v>0.5249999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>19.72875</v>
+        <v>19.17</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>0.49125</v>
+        <v>0.43125</v>
       </c>
       <c r="N4" t="n">
-        <v>18.67375</v>
+        <v>18.07</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.36</v>
+        <v>0.46375</v>
       </c>
       <c r="N5" t="n">
-        <v>18.72625</v>
+        <v>18.315</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.49</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4525</v>
+        <v>0.3475</v>
       </c>
       <c r="N6" t="n">
-        <v>18.1375</v>
+        <v>17.97125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.54</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3425</v>
+        <v>0.31</v>
       </c>
       <c r="N7" t="n">
-        <v>18.085</v>
+        <v>17.77625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.52</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3025</v>
+        <v>0.3075</v>
       </c>
       <c r="N8" t="n">
-        <v>17.19875</v>
+        <v>17.08875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.71</v>
       </c>
       <c r="M12" t="n">
-        <v>0.45</v>
+        <v>0.4500000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>19.17875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9924</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1860</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1506</v>
+      </c>
+      <c r="E75" t="n">
+        <v>354</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="G75" t="n">
+        <v>108</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.80%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>119</v>
+      </c>
+      <c r="K75" t="n">
+        <v>87</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.80875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.9975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.03999999999999992</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.07407407407407396</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.8800000000000026</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04417670682730934</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.289999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1473354231974922</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
